--- a/Dataset/IT/xlsx/ITAMed_2021.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2021.xlsx
@@ -640,7 +640,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Gastroenterologia</t>
+          <t>Gastroenterologia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Dermatologia e Venereologia; Chirurgia Generale</t>
+          <t>Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Ematologia; Oncologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>Endocrinologia; Farmacologia e Tossicologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>Nutrizione Clinica; Gastroenterologia</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Genetica Medica; Oncologia</t>
+          <t>Oncologia</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Cardiologia e Cardiochirurgia</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica</t>
+          <t>Pneumologia e Chirurgia Toracica; Malattie Infettive</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Pediatria</t>
+          <t>Malattie Infettive</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Gastroenterologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Igiene, Epidemiologia e Statistica</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L82" s="5" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>Dermatologia e Venereologia; Ginecologia e Ostetricia</t>
+          <t>Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L83" s="5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Pediatria</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L86" s="5" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t>Urologia; Oncologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L90" s="5" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Oftalmologia</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L93" s="5" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Endocrinologia</t>
+          <t>Otorinolaringoiatria; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L99" s="5" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Chirurgia Generale</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="K119" s="5" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Anestesia e Rianimazione</t>
+          <t>Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L119" s="5" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Pneumologia e Chirurgia Toracica</t>
+          <t>Pneumologia e Chirurgia Toracica; Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Cardiologia e Cardiochirurgia</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Oncologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L131" s="5" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="K135" s="5" t="inlineStr">
         <is>
-          <t>Medicina Legale; Igiene, Epidemiologia e Statistica</t>
+          <t>Igiene, Epidemiologia e Statistica; Medicina Legale</t>
         </is>
       </c>
       <c r="L135" s="5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>Medicina del Lavoro; Oncologia</t>
+          <t>Medicina del Lavoro</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="K138" s="5" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Medicina del Lavoro</t>
+          <t>Medicina del Lavoro; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L138" s="5" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
-          <t>Medicina Legale; Ginecologia e Ostetricia</t>
+          <t>Medicina Legale</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_2021.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2021.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
-          <t>Immagine</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" s="5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M2" s="5" t="n"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M3" s="5" t="n"/>
@@ -705,7 +705,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M5" s="5" t="n"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M6" s="5" t="n"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M7" s="5" t="n"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M8" s="5" t="n"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M9" s="5" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M10" s="5" t="n"/>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M11" s="5" t="n"/>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M12" s="5" t="n"/>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M13" s="5" t="n"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M14" s="5" t="n"/>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M15" s="5" t="n"/>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M16" s="5" t="n"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M17" s="5" t="n"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M18" s="5" t="n"/>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M19" s="5" t="n"/>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M20" s="5" t="n"/>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M21" s="5" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M22" s="5" t="n"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M23" s="5" t="n"/>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M24" s="5" t="n"/>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M25" s="5" t="n"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M26" s="5" t="n"/>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M27" s="5" t="n"/>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M28" s="5" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M29" s="5" t="n"/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M30" s="5" t="n"/>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M31" s="5" t="n"/>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M32" s="5" t="n"/>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M33" s="5" t="n"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M35" s="5" t="n"/>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M36" s="5" t="n"/>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M37" s="5" t="n"/>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M39" s="5" t="n"/>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M40" s="5" t="n"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M41" s="5" t="n"/>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M42" s="5" t="n"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M43" s="5" t="n"/>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M44" s="5" t="n"/>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M45" s="5" t="n"/>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M46" s="5" t="n"/>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M47" s="5" t="n"/>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M48" s="5" t="n"/>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M49" s="5" t="n"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M50" s="5" t="n"/>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M51" s="5" t="n"/>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M52" s="5" t="n"/>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M53" s="5" t="n"/>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M54" s="5" t="n"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M55" s="5" t="n"/>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M56" s="5" t="n"/>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M57" s="5" t="n"/>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M58" s="5" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M59" s="5" t="n"/>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M60" s="5" t="n"/>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M61" s="5" t="n"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M62" s="5" t="n"/>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M63" s="5" t="n"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M64" s="5" t="n"/>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M65" s="5" t="n"/>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M66" s="5" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M67" s="5" t="n"/>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M68" s="5" t="n"/>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M69" s="5" t="n"/>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M70" s="5" t="n"/>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M71" s="5" t="n"/>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M72" s="5" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M73" s="5" t="n"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M74" s="5" t="n"/>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M75" s="5" t="n"/>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M76" s="5" t="n"/>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M77" s="5" t="n"/>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M78" s="5" t="n"/>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M79" s="5" t="n"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M80" s="5" t="n"/>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M81" s="5" t="n"/>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M82" s="5" t="n"/>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M83" s="5" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M84" s="5" t="n"/>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M85" s="5" t="n"/>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M86" s="5" t="n"/>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M87" s="5" t="n"/>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M88" s="5" t="n"/>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M89" s="5" t="n"/>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M90" s="5" t="n"/>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M91" s="5" t="n"/>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M92" s="5" t="n"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M93" s="5" t="n"/>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M94" s="5" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M95" s="5" t="n"/>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M96" s="5" t="n"/>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M97" s="5" t="n"/>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M98" s="5" t="n"/>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M99" s="5" t="n"/>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M100" s="5" t="n"/>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M101" s="5" t="n"/>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M102" s="5" t="n"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M103" s="5" t="n"/>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M104" s="5" t="n"/>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M105" s="5" t="n"/>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M106" s="5" t="n"/>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M107" s="5" t="n"/>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M108" s="5" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M109" s="5" t="n"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M110" s="5" t="n"/>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M111" s="5" t="n"/>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M112" s="5" t="n"/>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M113" s="5" t="n"/>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M114" s="5" t="n"/>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M115" s="5" t="n"/>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M116" s="5" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M117" s="5" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M118" s="5" t="n"/>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M119" s="5" t="n"/>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M120" s="5" t="n"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M121" s="5" t="n"/>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M122" s="5" t="n"/>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M123" s="5" t="n"/>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M124" s="5" t="n"/>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M125" s="5" t="n"/>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M126" s="5" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M127" s="5" t="n"/>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M128" s="5" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M129" s="5" t="n"/>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M130" s="5" t="n"/>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M131" s="5" t="n"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M132" s="5" t="n"/>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M133" s="5" t="n"/>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M134" s="5" t="n"/>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M135" s="5" t="n"/>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M136" s="5" t="n"/>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M137" s="5" t="n"/>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M138" s="5" t="n"/>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M139" s="5" t="n"/>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M140" s="5" t="n"/>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M141" s="5" t="n"/>

--- a/Dataset/IT/xlsx/ITAMed_2021.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2021.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -517,15 +517,20 @@
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
-          <t>question_type</t>
-        </is>
-      </c>
-      <c r="M1" s="5" t="inlineStr">
+          <t>Tipo Domanda</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Immagine</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Categoria Immagine</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>Percorso Immagine</t>
         </is>
@@ -588,8 +593,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M2" s="5" t="n"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -648,8 +658,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M3" s="5" t="n"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="3" t="n">
@@ -708,12 +723,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Chest X-ray</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>images/2021/ssm202110228954.png</t>
         </is>
@@ -776,8 +796,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M5" s="5" t="n"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -836,8 +861,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M6" s="5" t="n"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -896,8 +926,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M7" s="5" t="n"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -956,8 +991,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M8" s="5" t="n"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -1016,8 +1056,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M9" s="5" t="n"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -1076,8 +1121,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M10" s="5" t="n"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -1136,8 +1186,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M11" s="5" t="n"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -1196,8 +1251,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M12" s="5" t="n"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -1256,8 +1316,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M13" s="5" t="n"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -1316,8 +1381,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M14" s="5" t="n"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -1376,8 +1446,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M15" s="5" t="n"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -1436,8 +1511,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M16" s="5" t="n"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -1496,8 +1576,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M17" s="5" t="n"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -1556,8 +1641,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M18" s="5" t="n"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -1616,8 +1706,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M19" s="5" t="n"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -1676,8 +1771,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M20" s="5" t="n"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -1736,8 +1836,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M21" s="5" t="n"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -1796,8 +1901,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M22" s="5" t="n"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -1856,8 +1966,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M23" s="5" t="n"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -1916,8 +2031,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M24" s="5" t="n"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -1976,8 +2096,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M25" s="5" t="n"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="3" t="n">
@@ -2036,8 +2161,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M26" s="5" t="n"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -2096,8 +2226,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M27" s="5" t="n"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="3" t="n">
@@ -2156,8 +2291,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M28" s="5" t="n"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -2216,8 +2356,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M29" s="5" t="n"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="3" t="n">
@@ -2276,8 +2421,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M30" s="5" t="n"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="3" t="n">
@@ -2336,8 +2486,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M31" s="5" t="n"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="3" t="n">
@@ -2396,8 +2551,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M32" s="5" t="n"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -2456,8 +2616,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M33" s="5" t="n"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="3" t="n">
@@ -2516,12 +2681,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>images/2021/ssm202110230454.png</t>
         </is>
@@ -2584,8 +2754,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M35" s="5" t="n"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="3" t="n">
@@ -2644,8 +2819,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M36" s="5" t="n"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="3" t="n">
@@ -2704,8 +2884,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M37" s="5" t="n"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="3" t="n">
@@ -2764,12 +2949,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>images/2021/ssm202110230654.png</t>
         </is>
@@ -2832,8 +3022,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M39" s="5" t="n"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="3" t="n">
@@ -2892,8 +3087,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M40" s="5" t="n"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="3" t="n">
@@ -2952,8 +3152,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M41" s="5" t="n"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="3" t="n">
@@ -3012,8 +3217,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M42" s="5" t="n"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="3" t="n">
@@ -3072,8 +3282,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M43" s="5" t="n"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="3" t="n">
@@ -3132,8 +3347,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M44" s="5" t="n"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="3" t="n">
@@ -3192,8 +3412,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M45" s="5" t="n"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="3" t="n">
@@ -3252,8 +3477,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M46" s="5" t="n"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="3" t="n">
@@ -3312,8 +3542,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M47" s="5" t="n"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="3" t="n">
@@ -3372,8 +3607,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M48" s="5" t="n"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="3" t="n">
@@ -3432,8 +3672,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M49" s="5" t="n"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="3" t="n">
@@ -3492,8 +3737,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M50" s="5" t="n"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="3" t="n">
@@ -3552,8 +3802,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M51" s="5" t="n"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="3" t="n">
@@ -3612,8 +3867,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M52" s="5" t="n"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
       <c r="A53" s="3" t="n">
@@ -3672,8 +3932,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M53" s="5" t="n"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="3" t="n">
@@ -3732,8 +3997,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M54" s="5" t="n"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="3" t="n">
@@ -3792,8 +4062,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M55" s="5" t="n"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" s="3" t="n">
@@ -3852,8 +4127,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M56" s="5" t="n"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
     </row>
     <row r="57" ht="18.75" customHeight="1">
       <c r="A57" s="3" t="n">
@@ -3912,8 +4192,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M57" s="5" t="n"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -3972,8 +4257,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M58" s="5" t="n"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" s="3" t="n">
@@ -4032,8 +4322,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M59" s="5" t="n"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" s="3" t="n">
@@ -4092,8 +4387,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M60" s="5" t="n"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
     </row>
     <row r="61" ht="18.75" customHeight="1">
       <c r="A61" s="3" t="n">
@@ -4152,8 +4452,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M61" s="5" t="n"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" s="3" t="n">
@@ -4212,8 +4517,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M62" s="5" t="n"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" s="3" t="n">
@@ -4272,8 +4582,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M63" s="5" t="n"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
     </row>
     <row r="64" ht="18.75" customHeight="1">
       <c r="A64" s="3" t="n">
@@ -4332,8 +4647,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M64" s="5" t="n"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
     </row>
     <row r="65" ht="18.75" customHeight="1">
       <c r="A65" s="3" t="n">
@@ -4392,8 +4712,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M65" s="5" t="n"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
     </row>
     <row r="66" ht="18.75" customHeight="1">
       <c r="A66" s="3" t="n">
@@ -4452,8 +4777,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M66" s="5" t="n"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
     </row>
     <row r="67" ht="18.75" customHeight="1">
       <c r="A67" s="3" t="n">
@@ -4512,8 +4842,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M67" s="5" t="n"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
     </row>
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" s="3" t="n">
@@ -4572,8 +4907,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M68" s="5" t="n"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N68" s="5" t="n"/>
+      <c r="O68" s="5" t="n"/>
     </row>
     <row r="69" ht="18.75" customHeight="1">
       <c r="A69" s="3" t="n">
@@ -4632,8 +4972,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M69" s="5" t="n"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N69" s="5" t="n"/>
+      <c r="O69" s="5" t="n"/>
     </row>
     <row r="70" ht="18.75" customHeight="1">
       <c r="A70" s="3" t="n">
@@ -4692,8 +5037,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M70" s="5" t="n"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
     </row>
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" s="3" t="n">
@@ -4752,8 +5102,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M71" s="5" t="n"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
       <c r="A72" s="3" t="n">
@@ -4812,8 +5167,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M72" s="5" t="n"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N72" s="5" t="n"/>
+      <c r="O72" s="5" t="n"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" s="3" t="n">
@@ -4872,8 +5232,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M73" s="5" t="n"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N73" s="5" t="n"/>
+      <c r="O73" s="5" t="n"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
       <c r="A74" s="3" t="n">
@@ -4932,8 +5297,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M74" s="5" t="n"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N74" s="5" t="n"/>
+      <c r="O74" s="5" t="n"/>
     </row>
     <row r="75" ht="18.75" customHeight="1">
       <c r="A75" s="3" t="n">
@@ -4992,8 +5362,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M75" s="5" t="n"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N75" s="5" t="n"/>
+      <c r="O75" s="5" t="n"/>
     </row>
     <row r="76" ht="18.75" customHeight="1">
       <c r="A76" s="3" t="n">
@@ -5052,8 +5427,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M76" s="5" t="n"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N76" s="5" t="n"/>
+      <c r="O76" s="5" t="n"/>
     </row>
     <row r="77" ht="18.75" customHeight="1">
       <c r="A77" s="3" t="n">
@@ -5112,8 +5492,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M77" s="5" t="n"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N77" s="5" t="n"/>
+      <c r="O77" s="5" t="n"/>
     </row>
     <row r="78" ht="18.75" customHeight="1">
       <c r="A78" s="3" t="n">
@@ -5172,8 +5557,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M78" s="5" t="n"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
     </row>
     <row r="79" ht="18.75" customHeight="1">
       <c r="A79" s="3" t="n">
@@ -5232,8 +5622,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M79" s="5" t="n"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N79" s="5" t="n"/>
+      <c r="O79" s="5" t="n"/>
     </row>
     <row r="80" ht="18.75" customHeight="1">
       <c r="A80" s="3" t="n">
@@ -5292,8 +5687,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M80" s="5" t="n"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N80" s="5" t="n"/>
+      <c r="O80" s="5" t="n"/>
     </row>
     <row r="81" ht="18.75" customHeight="1">
       <c r="A81" s="3" t="n">
@@ -5352,8 +5752,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M81" s="5" t="n"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N81" s="5" t="n"/>
+      <c r="O81" s="5" t="n"/>
     </row>
     <row r="82" ht="18.75" customHeight="1">
       <c r="A82" s="3" t="n">
@@ -5412,8 +5817,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M82" s="5" t="n"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N82" s="5" t="n"/>
+      <c r="O82" s="5" t="n"/>
     </row>
     <row r="83" ht="18.75" customHeight="1">
       <c r="A83" s="3" t="n">
@@ -5472,8 +5882,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M83" s="5" t="n"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
     </row>
     <row r="84" ht="18.75" customHeight="1">
       <c r="A84" s="3" t="n">
@@ -5532,8 +5947,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M84" s="5" t="n"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N84" s="5" t="n"/>
+      <c r="O84" s="5" t="n"/>
     </row>
     <row r="85" ht="18.75" customHeight="1">
       <c r="A85" s="3" t="n">
@@ -5592,8 +6012,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M85" s="5" t="n"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N85" s="5" t="n"/>
+      <c r="O85" s="5" t="n"/>
     </row>
     <row r="86" ht="18.75" customHeight="1">
       <c r="A86" s="3" t="n">
@@ -5652,8 +6077,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M86" s="5" t="n"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
     </row>
     <row r="87" ht="18.75" customHeight="1">
       <c r="A87" s="3" t="n">
@@ -5712,8 +6142,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M87" s="5" t="n"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
     </row>
     <row r="88" ht="18.75" customHeight="1">
       <c r="A88" s="3" t="n">
@@ -5772,8 +6207,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M88" s="5" t="n"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
     </row>
     <row r="89" ht="18.75" customHeight="1">
       <c r="A89" s="3" t="n">
@@ -5832,8 +6272,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M89" s="5" t="n"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
     </row>
     <row r="90" ht="18.75" customHeight="1">
       <c r="A90" s="3" t="n">
@@ -5892,8 +6337,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M90" s="5" t="n"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N90" s="5" t="n"/>
+      <c r="O90" s="5" t="n"/>
     </row>
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" s="3" t="n">
@@ -5952,8 +6402,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M91" s="5" t="n"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N91" s="5" t="n"/>
+      <c r="O91" s="5" t="n"/>
     </row>
     <row r="92" ht="18.75" customHeight="1">
       <c r="A92" s="3" t="n">
@@ -6012,8 +6467,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M92" s="5" t="n"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
     </row>
     <row r="93" ht="18.75" customHeight="1">
       <c r="A93" s="3" t="n">
@@ -6072,8 +6532,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M93" s="5" t="n"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
     </row>
     <row r="94" ht="18.75" customHeight="1">
       <c r="A94" s="3" t="n">
@@ -6132,12 +6597,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M94" s="5" t="inlineStr">
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N94" s="5" t="inlineStr">
         <is>
           <t>Fundus examination</t>
         </is>
       </c>
-      <c r="N94" s="5" t="inlineStr">
+      <c r="O94" s="5" t="inlineStr">
         <is>
           <t>images/2021/ssm202110233454.png</t>
         </is>
@@ -6200,8 +6670,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M95" s="5" t="n"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N95" s="5" t="n"/>
+      <c r="O95" s="5" t="n"/>
     </row>
     <row r="96" ht="18.75" customHeight="1">
       <c r="A96" s="3" t="n">
@@ -6260,8 +6735,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M96" s="5" t="n"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
     </row>
     <row r="97" ht="18.75" customHeight="1">
       <c r="A97" s="3" t="n">
@@ -6320,8 +6800,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M97" s="5" t="n"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N97" s="5" t="n"/>
+      <c r="O97" s="5" t="n"/>
     </row>
     <row r="98" ht="18.75" customHeight="1">
       <c r="A98" s="3" t="n">
@@ -6380,8 +6865,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M98" s="5" t="n"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
     </row>
     <row r="99" ht="18.75" customHeight="1">
       <c r="A99" s="3" t="n">
@@ -6440,8 +6930,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M99" s="5" t="n"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N99" s="5" t="n"/>
+      <c r="O99" s="5" t="n"/>
     </row>
     <row r="100" ht="18.75" customHeight="1">
       <c r="A100" s="3" t="n">
@@ -6500,8 +6995,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M100" s="5" t="n"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
     </row>
     <row r="101" ht="18.75" customHeight="1">
       <c r="A101" s="3" t="n">
@@ -6560,8 +7060,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M101" s="5" t="n"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N101" s="5" t="n"/>
+      <c r="O101" s="5" t="n"/>
     </row>
     <row r="102" ht="18.75" customHeight="1">
       <c r="A102" s="3" t="n">
@@ -6620,8 +7125,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M102" s="5" t="n"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N102" s="5" t="n"/>
+      <c r="O102" s="5" t="n"/>
     </row>
     <row r="103" ht="18.75" customHeight="1">
       <c r="A103" s="3" t="n">
@@ -6680,8 +7190,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M103" s="5" t="n"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N103" s="5" t="n"/>
+      <c r="O103" s="5" t="n"/>
     </row>
     <row r="104" ht="18.75" customHeight="1">
       <c r="A104" s="3" t="n">
@@ -6740,8 +7255,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M104" s="5" t="n"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N104" s="5" t="n"/>
+      <c r="O104" s="5" t="n"/>
     </row>
     <row r="105" ht="18.75" customHeight="1">
       <c r="A105" s="3" t="n">
@@ -6800,8 +7320,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M105" s="5" t="n"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
     </row>
     <row r="106" ht="18.75" customHeight="1">
       <c r="A106" s="3" t="n">
@@ -6860,8 +7385,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M106" s="5" t="n"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N106" s="5" t="n"/>
+      <c r="O106" s="5" t="n"/>
     </row>
     <row r="107" ht="18.75" customHeight="1">
       <c r="A107" s="3" t="n">
@@ -6920,8 +7450,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M107" s="5" t="n"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
     </row>
     <row r="108" ht="18.75" customHeight="1">
       <c r="A108" s="3" t="n">
@@ -6980,8 +7515,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M108" s="5" t="n"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N108" s="5" t="n"/>
+      <c r="O108" s="5" t="n"/>
     </row>
     <row r="109" ht="18.75" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -7040,8 +7580,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M109" s="5" t="n"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N109" s="5" t="n"/>
+      <c r="O109" s="5" t="n"/>
     </row>
     <row r="110" ht="18.75" customHeight="1">
       <c r="A110" s="3" t="n">
@@ -7100,8 +7645,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M110" s="5" t="n"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N110" s="5" t="n"/>
+      <c r="O110" s="5" t="n"/>
     </row>
     <row r="111" ht="18.75" customHeight="1">
       <c r="A111" s="3" t="n">
@@ -7160,8 +7710,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M111" s="5" t="n"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N111" s="5" t="n"/>
+      <c r="O111" s="5" t="n"/>
     </row>
     <row r="112" ht="18.75" customHeight="1">
       <c r="A112" s="3" t="n">
@@ -7220,8 +7775,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M112" s="5" t="n"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N112" s="5" t="n"/>
+      <c r="O112" s="5" t="n"/>
     </row>
     <row r="113" ht="18.75" customHeight="1">
       <c r="A113" s="3" t="n">
@@ -7280,8 +7840,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M113" s="5" t="n"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N113" s="5" t="n"/>
+      <c r="O113" s="5" t="n"/>
     </row>
     <row r="114" ht="18.75" customHeight="1">
       <c r="A114" s="3" t="n">
@@ -7340,8 +7905,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M114" s="5" t="n"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N114" s="5" t="n"/>
+      <c r="O114" s="5" t="n"/>
     </row>
     <row r="115" ht="18.75" customHeight="1">
       <c r="A115" s="3" t="n">
@@ -7400,8 +7970,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M115" s="5" t="n"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N115" s="5" t="n"/>
+      <c r="O115" s="5" t="n"/>
     </row>
     <row r="116" ht="18.75" customHeight="1">
       <c r="A116" s="3" t="n">
@@ -7460,12 +8035,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M116" s="5" t="inlineStr">
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N116" s="5" t="inlineStr">
         <is>
           <t>Lower limb X-ray</t>
         </is>
       </c>
-      <c r="N116" s="5" t="inlineStr">
+      <c r="O116" s="5" t="inlineStr">
         <is>
           <t>images/2021/ssm202110234554.png</t>
         </is>
@@ -7528,12 +8108,17 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M117" s="5" t="inlineStr">
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N117" s="5" t="inlineStr">
         <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N117" s="5" t="inlineStr">
+      <c r="O117" s="5" t="inlineStr">
         <is>
           <t>images/2021/ssm202110234604.png</t>
         </is>
@@ -7596,8 +8181,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M118" s="5" t="n"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N118" s="5" t="n"/>
+      <c r="O118" s="5" t="n"/>
     </row>
     <row r="119" ht="18.75" customHeight="1">
       <c r="A119" s="3" t="n">
@@ -7656,8 +8246,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M119" s="5" t="n"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N119" s="5" t="n"/>
+      <c r="O119" s="5" t="n"/>
     </row>
     <row r="120" ht="18.75" customHeight="1">
       <c r="A120" s="3" t="n">
@@ -7716,8 +8311,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M120" s="5" t="n"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N120" s="5" t="n"/>
+      <c r="O120" s="5" t="n"/>
     </row>
     <row r="121" ht="18.75" customHeight="1">
       <c r="A121" s="3" t="n">
@@ -7776,8 +8376,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M121" s="5" t="n"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N121" s="5" t="n"/>
+      <c r="O121" s="5" t="n"/>
     </row>
     <row r="122" ht="18.75" customHeight="1">
       <c r="A122" s="3" t="n">
@@ -7836,8 +8441,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M122" s="5" t="n"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N122" s="5" t="n"/>
+      <c r="O122" s="5" t="n"/>
     </row>
     <row r="123" ht="18.75" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -7896,8 +8506,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M123" s="5" t="n"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N123" s="5" t="n"/>
+      <c r="O123" s="5" t="n"/>
     </row>
     <row r="124" ht="18.75" customHeight="1">
       <c r="A124" s="3" t="n">
@@ -7956,8 +8571,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M124" s="5" t="n"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N124" s="5" t="n"/>
+      <c r="O124" s="5" t="n"/>
     </row>
     <row r="125" ht="18.75" customHeight="1">
       <c r="A125" s="3" t="n">
@@ -8016,8 +8636,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M125" s="5" t="n"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N125" s="5" t="n"/>
+      <c r="O125" s="5" t="n"/>
     </row>
     <row r="126" ht="18.75" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -8076,8 +8701,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M126" s="5" t="n"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N126" s="5" t="n"/>
+      <c r="O126" s="5" t="n"/>
     </row>
     <row r="127" ht="18.75" customHeight="1">
       <c r="A127" s="3" t="n">
@@ -8136,8 +8766,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M127" s="5" t="n"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N127" s="5" t="n"/>
+      <c r="O127" s="5" t="n"/>
     </row>
     <row r="128" ht="18.75" customHeight="1">
       <c r="A128" s="3" t="n">
@@ -8196,8 +8831,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M128" s="5" t="n"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N128" s="5" t="n"/>
+      <c r="O128" s="5" t="n"/>
     </row>
     <row r="129" ht="18.75" customHeight="1">
       <c r="A129" s="3" t="n">
@@ -8256,8 +8896,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M129" s="5" t="n"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N129" s="5" t="n"/>
+      <c r="O129" s="5" t="n"/>
     </row>
     <row r="130" ht="18.75" customHeight="1">
       <c r="A130" s="3" t="n">
@@ -8316,8 +8961,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M130" s="5" t="n"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N130" s="5" t="n"/>
+      <c r="O130" s="5" t="n"/>
     </row>
     <row r="131" ht="18.75" customHeight="1">
       <c r="A131" s="3" t="n">
@@ -8376,8 +9026,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M131" s="5" t="n"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N131" s="5" t="n"/>
+      <c r="O131" s="5" t="n"/>
     </row>
     <row r="132" ht="18.75" customHeight="1">
       <c r="A132" s="3" t="n">
@@ -8436,8 +9091,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M132" s="5" t="n"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N132" s="5" t="n"/>
+      <c r="O132" s="5" t="n"/>
     </row>
     <row r="133" ht="18.75" customHeight="1">
       <c r="A133" s="3" t="n">
@@ -8496,8 +9156,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M133" s="5" t="n"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N133" s="5" t="n"/>
+      <c r="O133" s="5" t="n"/>
     </row>
     <row r="134" ht="18.75" customHeight="1">
       <c r="A134" s="3" t="n">
@@ -8556,8 +9221,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M134" s="5" t="n"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N134" s="5" t="n"/>
+      <c r="O134" s="5" t="n"/>
     </row>
     <row r="135" ht="18.75" customHeight="1">
       <c r="A135" s="3" t="n">
@@ -8616,8 +9286,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M135" s="5" t="n"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N135" s="5" t="n"/>
+      <c r="O135" s="5" t="n"/>
     </row>
     <row r="136" ht="18.75" customHeight="1">
       <c r="A136" s="3" t="n">
@@ -8676,8 +9351,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M136" s="5" t="n"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N136" s="5" t="n"/>
+      <c r="O136" s="5" t="n"/>
     </row>
     <row r="137" ht="18.75" customHeight="1">
       <c r="A137" s="3" t="n">
@@ -8736,8 +9416,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M137" s="5" t="n"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N137" s="5" t="n"/>
+      <c r="O137" s="5" t="n"/>
     </row>
     <row r="138" ht="18.75" customHeight="1">
       <c r="A138" s="3" t="n">
@@ -8796,8 +9481,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M138" s="5" t="n"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N138" s="5" t="n"/>
+      <c r="O138" s="5" t="n"/>
     </row>
     <row r="139" ht="18.75" customHeight="1">
       <c r="A139" s="3" t="n">
@@ -8856,8 +9546,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M139" s="5" t="n"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N139" s="5" t="n"/>
+      <c r="O139" s="5" t="n"/>
     </row>
     <row r="140" ht="18.75" customHeight="1">
       <c r="A140" s="3" t="n">
@@ -8916,8 +9611,13 @@
           <t>case-based</t>
         </is>
       </c>
-      <c r="M140" s="5" t="n"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N140" s="5" t="n"/>
+      <c r="O140" s="5" t="n"/>
     </row>
     <row r="141" ht="18.75" customHeight="1">
       <c r="A141" s="3" t="n">
@@ -8976,8 +9676,13 @@
           <t>knowledge-based</t>
         </is>
       </c>
-      <c r="M141" s="5" t="n"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N141" s="5" t="n"/>
+      <c r="O141" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
